--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748506</v>
+        <v>121748515</v>
       </c>
       <c r="B2" t="n">
         <v>74661</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702748</v>
+        <v>702752</v>
       </c>
       <c r="R2" t="n">
-        <v>6627081</v>
+        <v>6627080</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121748515</v>
+        <v>121748506</v>
       </c>
       <c r="B4" t="n">
         <v>74661</v>
@@ -970,14 +970,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702752</v>
+        <v>702748</v>
       </c>
       <c r="R4" t="n">
-        <v>6627080</v>
+        <v>6627081</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121841210</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74706</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordbrant oppsjön , Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>702735</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6627084</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748515</v>
+        <v>121750568</v>
       </c>
       <c r="B2" t="n">
         <v>74661</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702752</v>
+        <v>702749</v>
       </c>
       <c r="R2" t="n">
-        <v>6627080</v>
+        <v>6627095</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121750568</v>
+        <v>121748515</v>
       </c>
       <c r="B3" t="n">
         <v>74661</v>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön, Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702749</v>
+        <v>702752</v>
       </c>
       <c r="R3" t="n">
-        <v>6627095</v>
+        <v>6627080</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121750568</v>
+        <v>121748515</v>
       </c>
       <c r="B2" t="n">
         <v>74661</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön, Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702749</v>
+        <v>702752</v>
       </c>
       <c r="R2" t="n">
-        <v>6627095</v>
+        <v>6627080</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121748515</v>
+        <v>121750568</v>
       </c>
       <c r="B3" t="n">
         <v>74661</v>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702752</v>
+        <v>702749</v>
       </c>
       <c r="R3" t="n">
-        <v>6627080</v>
+        <v>6627095</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121750568</v>
+        <v>121748506</v>
       </c>
       <c r="B2" t="n">
         <v>74661</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702749</v>
+        <v>702748</v>
       </c>
       <c r="R2" t="n">
-        <v>6627095</v>
+        <v>6627081</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121748506</v>
+        <v>121750568</v>
       </c>
       <c r="B4" t="n">
         <v>74661</v>
@@ -970,14 +970,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702748</v>
+        <v>702749</v>
       </c>
       <c r="R4" t="n">
-        <v>6627081</v>
+        <v>6627095</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748506</v>
+        <v>121748515</v>
       </c>
       <c r="B2" t="n">
         <v>74661</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702748</v>
+        <v>702752</v>
       </c>
       <c r="R2" t="n">
-        <v>6627081</v>
+        <v>6627080</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121748515</v>
+        <v>121748506</v>
       </c>
       <c r="B3" t="n">
         <v>74661</v>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702752</v>
+        <v>702748</v>
       </c>
       <c r="R3" t="n">
-        <v>6627080</v>
+        <v>6627081</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748515</v>
+        <v>121748506</v>
       </c>
       <c r="B2" t="n">
-        <v>74661</v>
+        <v>74674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702752</v>
+        <v>702748</v>
       </c>
       <c r="R2" t="n">
-        <v>6627080</v>
+        <v>6627081</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121748506</v>
+        <v>121748515</v>
       </c>
       <c r="B3" t="n">
-        <v>74661</v>
+        <v>74674</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702748</v>
+        <v>702752</v>
       </c>
       <c r="R3" t="n">
-        <v>6627081</v>
+        <v>6627080</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>121750568</v>
       </c>
       <c r="B4" t="n">
-        <v>74661</v>
+        <v>74674</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>121841210</v>
       </c>
       <c r="B5" t="n">
-        <v>74706</v>
+        <v>74719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121748506</v>
       </c>
       <c r="B2" t="n">
-        <v>74674</v>
+        <v>74676</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>121748515</v>
       </c>
       <c r="B3" t="n">
-        <v>74674</v>
+        <v>74676</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121750568</v>
       </c>
       <c r="B4" t="n">
-        <v>74674</v>
+        <v>74676</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>121841210</v>
       </c>
       <c r="B5" t="n">
-        <v>74719</v>
+        <v>74721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748506</v>
+        <v>121750568</v>
       </c>
       <c r="B2" t="n">
         <v>74676</v>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702748</v>
+        <v>702749</v>
       </c>
       <c r="R2" t="n">
-        <v>6627081</v>
+        <v>6627095</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121750568</v>
+        <v>121748506</v>
       </c>
       <c r="B4" t="n">
         <v>74676</v>
@@ -970,14 +970,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702749</v>
+        <v>702748</v>
       </c>
       <c r="R4" t="n">
-        <v>6627095</v>
+        <v>6627081</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121750568</v>
+        <v>121748515</v>
       </c>
       <c r="B2" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön, Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702749</v>
+        <v>702752</v>
       </c>
       <c r="R2" t="n">
-        <v>6627095</v>
+        <v>6627080</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121748515</v>
+        <v>121748506</v>
       </c>
       <c r="B3" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702752</v>
+        <v>702748</v>
       </c>
       <c r="R3" t="n">
-        <v>6627080</v>
+        <v>6627081</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121748506</v>
+        <v>121750568</v>
       </c>
       <c r="B4" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,14 +970,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702748</v>
+        <v>702749</v>
       </c>
       <c r="R4" t="n">
-        <v>6627081</v>
+        <v>6627095</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>121841210</v>
       </c>
       <c r="B5" t="n">
-        <v>74721</v>
+        <v>74725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121748515</v>
+        <v>121748506</v>
       </c>
       <c r="B2" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön 1, Upl</t>
+          <t>Nordbrant oppsjön , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702752</v>
+        <v>702748</v>
       </c>
       <c r="R2" t="n">
-        <v>6627080</v>
+        <v>6627081</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121748506</v>
+        <v>121748515</v>
       </c>
       <c r="B3" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbrant oppsjön , Upl</t>
+          <t>Nordbrant oppsjön 1, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702748</v>
+        <v>702752</v>
       </c>
       <c r="R3" t="n">
-        <v>6627081</v>
+        <v>6627080</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>121750568</v>
       </c>
       <c r="B4" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>121841210</v>
       </c>
       <c r="B5" t="n">
-        <v>74725</v>
+        <v>74729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23583-2024 artfynd.xlsx
+++ b/artfynd/A 23583-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>121841210</v>
       </c>
       <c r="B5" t="n">
-        <v>74729</v>
+        <v>74731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
